--- a/data/trans_orig/P16A13-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A13-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8666</t>
+          <t>7954</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25295</t>
+          <t>24371</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>11829</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13325</t>
+          <t>13676</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32229</t>
+          <t>34021</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>448481</t>
+          <t>449405</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>465110</t>
+          <t>465822</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294632</t>
+          <t>294851</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>303998</t>
+          <t>304717</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>748228</t>
+          <t>746436</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>767132</t>
+          <t>766781</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16747</t>
+          <t>17026</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19751</t>
+          <t>19700</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12700</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31371</t>
+          <t>29246</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>350187</t>
+          <t>349908</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363045</t>
+          <t>363295</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>352114</t>
+          <t>352165</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>365720</t>
+          <t>365921</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>707428</t>
+          <t>709553</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>726099</t>
+          <t>726545</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6408</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20691</t>
+          <t>20168</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16079</t>
+          <t>16212</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13523</t>
+          <t>13094</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31072</t>
+          <t>30403</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>521698</t>
+          <t>522221</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>535981</t>
+          <t>535818</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>151703</t>
+          <t>151570</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163895</t>
+          <t>163034</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>679099</t>
+          <t>679768</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>696648</t>
+          <t>697077</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28135</t>
+          <t>25755</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52019</t>
+          <t>51437</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13723</t>
+          <t>13672</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31107</t>
+          <t>31624</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44795</t>
+          <t>45268</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74717</t>
+          <t>75652</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1186315</t>
+          <t>1186897</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1210199</t>
+          <t>1212579</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>683178</t>
+          <t>682661</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>700562</t>
+          <t>700613</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1877903</t>
+          <t>1876968</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1907825</t>
+          <t>1907352</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5817</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19406</t>
+          <t>19265</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10060</t>
+          <t>10388</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26974</t>
+          <t>26324</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19933</t>
+          <t>19290</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41024</t>
+          <t>40028</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>330131</t>
+          <t>330272</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>343720</t>
+          <t>343386</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>541778</t>
+          <t>542428</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>558692</t>
+          <t>558364</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>877265</t>
+          <t>878261</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>898356</t>
+          <t>898999</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43526</t>
+          <t>43211</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>74266</t>
+          <t>72317</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44773</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75638</t>
+          <t>76218</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>291461</t>
+          <t>291763</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1174494</t>
+          <t>1176443</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1205234</t>
+          <t>1205549</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1471322</t>
+          <t>1470742</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1502187</t>
+          <t>1501299</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>69958</t>
+          <t>68687</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>106641</t>
+          <t>105792</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>101175</t>
+          <t>99801</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>145504</t>
+          <t>142997</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>181637</t>
+          <t>179873</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>240278</t>
+          <t>236167</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3162531</t>
+          <t>3163380</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3199214</t>
+          <t>3200485</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3232620</t>
+          <t>3235127</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3276949</t>
+          <t>3278323</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6407018</t>
+          <t>6411129</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6465659</t>
+          <t>6467423</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10096</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31459</t>
+          <t>33174</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11263</t>
+          <t>11171</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29502</t>
+          <t>28979</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25239</t>
+          <t>26274</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54546</t>
+          <t>53997</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>405752</t>
+          <t>404037</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427115</t>
+          <t>426339</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>284952</t>
+          <t>285475</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>303191</t>
+          <t>303283</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>697119</t>
+          <t>697668</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>726426</t>
+          <t>725391</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,5%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>7096</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24940</t>
+          <t>23639</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25943</t>
+          <t>26088</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18909</t>
+          <t>19272</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44713</t>
+          <t>43225</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>392078</t>
+          <t>393379</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>410088</t>
+          <t>409922</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>309372</t>
+          <t>309227</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>326810</t>
+          <t>326769</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>707620</t>
+          <t>709108</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>733424</t>
+          <t>733061</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13178</t>
+          <t>12986</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33032</t>
+          <t>32496</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20539</t>
+          <t>20974</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23989</t>
+          <t>22243</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46713</t>
+          <t>46872</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>592216</t>
+          <t>592752</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>612070</t>
+          <t>612262</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>237399</t>
+          <t>236964</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>252105</t>
+          <t>251874</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>836473</t>
+          <t>836314</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>859197</t>
+          <t>860943</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46303</t>
+          <t>46779</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78633</t>
+          <t>78431</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23907</t>
+          <t>22763</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47836</t>
+          <t>47094</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77510</t>
+          <t>76774</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116625</t>
+          <t>115730</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1076409</t>
+          <t>1076611</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1108739</t>
+          <t>1108263</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>718821</t>
+          <t>719563</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>742750</t>
+          <t>743894</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1805075</t>
+          <t>1805970</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1844190</t>
+          <t>1844926</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11603</t>
+          <t>12342</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30959</t>
+          <t>31103</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39719</t>
+          <t>39129</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69364</t>
+          <t>69720</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>55597</t>
+          <t>55715</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90262</t>
+          <t>91444</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>479637</t>
+          <t>479493</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>498993</t>
+          <t>498254</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>689941</t>
+          <t>689585</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>719586</t>
+          <t>720176</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1179639</t>
+          <t>1178457</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1214304</t>
+          <t>1214186</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13713</t>
+          <t>12783</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43525</t>
+          <t>43822</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72388</t>
+          <t>73198</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48163</t>
+          <t>47515</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79896</t>
+          <t>81176</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252128</t>
+          <t>253058</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263974</t>
+          <t>264504</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1032868</t>
+          <t>1032058</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1061731</t>
+          <t>1061434</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1291202</t>
+          <t>1289922</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1322935</t>
+          <t>1323583</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>119301</t>
+          <t>116721</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>169002</t>
+          <t>166001</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>161993</t>
+          <t>164149</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>220762</t>
+          <t>215562</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>295244</t>
+          <t>293285</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>369490</t>
+          <t>367589</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3241954</t>
+          <t>3244955</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3291655</t>
+          <t>3294235</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3318164</t>
+          <t>3323364</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3376933</t>
+          <t>3374777</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6580391</t>
+          <t>6582292</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6654637</t>
+          <t>6656596</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11043</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29774</t>
+          <t>29159</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5113</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20603</t>
+          <t>20794</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19418</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43633</t>
+          <t>43425</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>399318</t>
+          <t>399933</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>418049</t>
+          <t>417996</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>326452</t>
+          <t>326261</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>341942</t>
+          <t>341921</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>732514</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>756729</t>
+          <t>756784</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6868</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21543</t>
+          <t>21565</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8792</t>
+          <t>8997</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28244</t>
+          <t>26868</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>18380</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41672</t>
+          <t>42709</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>355684</t>
+          <t>355662</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>370359</t>
+          <t>370733</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>344029</t>
+          <t>345405</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363481</t>
+          <t>363276</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>707828</t>
+          <t>706791</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>731094</t>
+          <t>731120</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8650</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24904</t>
+          <t>25478</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19171</t>
+          <t>19486</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16555</t>
+          <t>16711</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38632</t>
+          <t>38877</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>497010</t>
+          <t>496436</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>513615</t>
+          <t>513264</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146952</t>
+          <t>146637</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161844</t>
+          <t>161683</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>649404</t>
+          <t>649159</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>671481</t>
+          <t>671325</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15914</t>
+          <t>15780</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35150</t>
+          <t>35553</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20629</t>
+          <t>20849</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43187</t>
+          <t>45381</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41699</t>
+          <t>40314</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69449</t>
+          <t>70302</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1114488</t>
+          <t>1114085</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1133724</t>
+          <t>1133858</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>782689</t>
+          <t>780495</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>805247</t>
+          <t>805027</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1906065</t>
+          <t>1905212</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1933815</t>
+          <t>1935200</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17986</t>
+          <t>17212</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39071</t>
+          <t>37819</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17552</t>
+          <t>16902</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39993</t>
+          <t>39654</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39522</t>
+          <t>40250</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68973</t>
+          <t>69233</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>581635</t>
+          <t>582887</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>602720</t>
+          <t>603494</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>698251</t>
+          <t>698590</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>720692</t>
+          <t>721342</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1289977</t>
+          <t>1289717</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1319428</t>
+          <t>1318700</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36150</t>
+          <t>36448</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65921</t>
+          <t>66754</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37082</t>
+          <t>36500</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>68261</t>
+          <t>67508</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>282278</t>
+          <t>281195</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1016104</t>
+          <t>1015271</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1045875</t>
+          <t>1045577</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1300909</t>
+          <t>1301662</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1332088</t>
+          <t>1332670</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>79710</t>
+          <t>78676</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>121298</t>
+          <t>118530</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>120198</t>
+          <t>121427</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>171532</t>
+          <t>171555</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>211402</t>
+          <t>213182</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>275323</t>
+          <t>276902</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3264424</t>
+          <t>3267192</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3306012</t>
+          <t>3307046</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3360064</t>
+          <t>3360041</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3411398</t>
+          <t>3410169</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6641995</t>
+          <t>6640416</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6705916</t>
+          <t>6704136</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27480</t>
+          <t>27951</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47639</t>
+          <t>48348</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14024</t>
+          <t>13970</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26637</t>
+          <t>26946</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44906</t>
+          <t>44935</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68596</t>
+          <t>68404</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>457573</t>
+          <t>456864</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>477732</t>
+          <t>477261</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>420830</t>
+          <t>420521</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>433443</t>
+          <t>433497</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>884083</t>
+          <t>884275</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>907773</t>
+          <t>907744</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18121</t>
+          <t>18329</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36933</t>
+          <t>36883</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12660</t>
+          <t>13184</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27338</t>
+          <t>26718</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34670</t>
+          <t>33312</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56744</t>
+          <t>56072</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415280</t>
+          <t>415330</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>434092</t>
+          <t>433884</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>355242</t>
+          <t>355862</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369920</t>
+          <t>369396</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>778049</t>
+          <t>778721</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>800123</t>
+          <t>801481</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12301</t>
+          <t>13011</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60045</t>
+          <t>60909</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14061</t>
+          <t>13908</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25504</t>
+          <t>25495</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23808</t>
+          <t>23751</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80114</t>
+          <t>80450</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>608219</t>
+          <t>607355</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>655963</t>
+          <t>655253</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141407</t>
+          <t>141416</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>152850</t>
+          <t>153003</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>755061</t>
+          <t>754725</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>811367</t>
+          <t>811424</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53633</t>
+          <t>53381</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80644</t>
+          <t>81666</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30623</t>
+          <t>26109</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75798</t>
+          <t>76642</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80319</t>
+          <t>83707</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>145734</t>
+          <t>145208</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>954175</t>
+          <t>953153</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>981186</t>
+          <t>981438</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>901730</t>
+          <t>900886</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>946905</t>
+          <t>951419</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1866613</t>
+          <t>1867139</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1932028</t>
+          <t>1928640</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25127</t>
+          <t>24361</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>54376</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67435</t>
+          <t>67696</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>109886</t>
+          <t>109660</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>103911</t>
+          <t>101696</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>150463</t>
+          <t>150600</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>418148</t>
+          <t>419673</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>448922</t>
+          <t>449688</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>729110</t>
+          <t>729336</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>771561</t>
+          <t>771300</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1162582</t>
+          <t>1162445</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1209134</t>
+          <t>1211349</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,25%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8666</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>64642</t>
+          <t>65039</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88683</t>
+          <t>89369</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>68252</t>
+          <t>67558</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>93263</t>
+          <t>94384</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>231841</t>
+          <t>231567</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239335</t>
+          <t>239292</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>671469</t>
+          <t>670783</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>695510</t>
+          <t>695113</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>907396</t>
+          <t>906275</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>932407</t>
+          <t>933101</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>158425</t>
+          <t>159567</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>233822</t>
+          <t>235617</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>234246</t>
+          <t>226022</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>316297</t>
+          <t>314157</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>425624</t>
+          <t>418661</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>534506</t>
+          <t>532388</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3141242</t>
+          <t>3139447</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3216639</t>
+          <t>3215497</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3257337</t>
+          <t>3259477</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3339388</t>
+          <t>3347612</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6414191</t>
+          <t>6416309</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6523073</t>
+          <t>6530036</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A13-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A13-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7954</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24371</t>
+          <t>24422</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11829</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13676</t>
+          <t>12925</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34021</t>
+          <t>31344</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449405</t>
+          <t>449354</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>465822</t>
+          <t>465024</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294851</t>
+          <t>294241</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304717</t>
+          <t>304629</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>746436</t>
+          <t>749113</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>766781</t>
+          <t>767532</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17026</t>
+          <t>15831</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5944</t>
+          <t>6071</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19700</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12254</t>
+          <t>11387</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29246</t>
+          <t>29476</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>349908</t>
+          <t>351103</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363295</t>
+          <t>363139</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>352165</t>
+          <t>352948</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>365921</t>
+          <t>365794</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>709553</t>
+          <t>709323</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>726545</t>
+          <t>727412</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20168</t>
+          <t>20689</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16212</t>
+          <t>16238</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13094</t>
+          <t>13266</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30403</t>
+          <t>30721</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>522221</t>
+          <t>521700</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>535818</t>
+          <t>535736</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>151570</t>
+          <t>151544</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163034</t>
+          <t>163875</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>679768</t>
+          <t>679450</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>697077</t>
+          <t>696905</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25755</t>
+          <t>27295</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51437</t>
+          <t>51099</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13672</t>
+          <t>14100</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31624</t>
+          <t>31063</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45268</t>
+          <t>43714</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75652</t>
+          <t>74080</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1186897</t>
+          <t>1187235</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1212579</t>
+          <t>1211039</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>682661</t>
+          <t>683222</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>700613</t>
+          <t>700185</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1876968</t>
+          <t>1878540</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1907352</t>
+          <t>1908906</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19265</t>
+          <t>19720</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10388</t>
+          <t>11400</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26324</t>
+          <t>29678</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19290</t>
+          <t>19511</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40028</t>
+          <t>41651</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>330272</t>
+          <t>329817</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>343386</t>
+          <t>343400</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>542428</t>
+          <t>539074</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>558364</t>
+          <t>557352</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>878261</t>
+          <t>876638</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>898999</t>
+          <t>898778</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6438</t>
+          <t>7163</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43211</t>
+          <t>43072</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72317</t>
+          <t>73076</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45661</t>
+          <t>45882</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76218</t>
+          <t>75912</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>291763</t>
+          <t>291038</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1176443</t>
+          <t>1175684</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1205549</t>
+          <t>1205688</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1470742</t>
+          <t>1471048</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1501299</t>
+          <t>1501078</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>68687</t>
+          <t>70269</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>105792</t>
+          <t>108235</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>99801</t>
+          <t>101258</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>142997</t>
+          <t>144108</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>179873</t>
+          <t>180819</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>236167</t>
+          <t>236869</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3163380</t>
+          <t>3160937</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3200485</t>
+          <t>3198903</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3235127</t>
+          <t>3234016</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3278323</t>
+          <t>3276866</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6411129</t>
+          <t>6410427</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6467423</t>
+          <t>6466477</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10872</t>
+          <t>11108</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33174</t>
+          <t>30817</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11171</t>
+          <t>11299</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28979</t>
+          <t>28529</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26274</t>
+          <t>25843</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53997</t>
+          <t>53843</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>404037</t>
+          <t>406394</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>426339</t>
+          <t>426103</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>285475</t>
+          <t>285925</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>303283</t>
+          <t>303155</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>697668</t>
+          <t>697822</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>725391</t>
+          <t>725822</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23639</t>
+          <t>23590</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8546</t>
+          <t>8542</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26088</t>
+          <t>26809</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19272</t>
+          <t>19084</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43225</t>
+          <t>43005</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>393379</t>
+          <t>393428</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>409922</t>
+          <t>410696</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>309227</t>
+          <t>308506</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>326769</t>
+          <t>326773</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>709108</t>
+          <t>709328</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>733061</t>
+          <t>733249</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12986</t>
+          <t>13358</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32496</t>
+          <t>32122</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>5972</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20974</t>
+          <t>20373</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22243</t>
+          <t>23443</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46872</t>
+          <t>46919</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>592752</t>
+          <t>593126</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>612262</t>
+          <t>611890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>236964</t>
+          <t>237565</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>251874</t>
+          <t>251966</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>836314</t>
+          <t>836267</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>860943</t>
+          <t>859743</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46779</t>
+          <t>47363</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78431</t>
+          <t>78254</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22763</t>
+          <t>22639</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47094</t>
+          <t>48359</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76774</t>
+          <t>77513</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115730</t>
+          <t>117317</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1076611</t>
+          <t>1076788</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1108263</t>
+          <t>1107679</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>719563</t>
+          <t>718298</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>743894</t>
+          <t>744018</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1805970</t>
+          <t>1804383</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1844926</t>
+          <t>1844187</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12342</t>
+          <t>12293</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31103</t>
+          <t>31260</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39129</t>
+          <t>39577</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69720</t>
+          <t>67655</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>55715</t>
+          <t>56889</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91444</t>
+          <t>91092</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>479493</t>
+          <t>479336</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>498254</t>
+          <t>498303</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>689585</t>
+          <t>691650</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>720176</t>
+          <t>719728</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1178457</t>
+          <t>1178809</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1214186</t>
+          <t>1213012</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12783</t>
+          <t>11721</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43822</t>
+          <t>44058</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73198</t>
+          <t>73021</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47515</t>
+          <t>47466</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81176</t>
+          <t>78360</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253058</t>
+          <t>254120</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264504</t>
+          <t>264818</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1032058</t>
+          <t>1032235</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1061434</t>
+          <t>1061198</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1289922</t>
+          <t>1292738</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1323583</t>
+          <t>1323632</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>116721</t>
+          <t>114404</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>166001</t>
+          <t>167069</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>164149</t>
+          <t>160010</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>215562</t>
+          <t>219109</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>293285</t>
+          <t>295467</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>367589</t>
+          <t>367454</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3244955</t>
+          <t>3243887</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3294235</t>
+          <t>3296552</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3323364</t>
+          <t>3319817</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3374777</t>
+          <t>3378916</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6582292</t>
+          <t>6582427</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6656596</t>
+          <t>6654414</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>10716</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29159</t>
+          <t>28723</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20794</t>
+          <t>20129</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19363</t>
+          <t>19628</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43425</t>
+          <t>43335</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>399933</t>
+          <t>400369</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>417996</t>
+          <t>418376</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>326261</t>
+          <t>326926</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>341921</t>
+          <t>342212</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>732722</t>
+          <t>732812</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>756784</t>
+          <t>756519</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>6081</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21565</t>
+          <t>20827</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8997</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26868</t>
+          <t>26264</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18380</t>
+          <t>18639</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42709</t>
+          <t>41597</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>355662</t>
+          <t>356400</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>370733</t>
+          <t>371146</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>345405</t>
+          <t>346009</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363276</t>
+          <t>363925</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>706791</t>
+          <t>707903</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>731120</t>
+          <t>730861</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8650</t>
+          <t>8684</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25478</t>
+          <t>25061</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19486</t>
+          <t>19518</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16711</t>
+          <t>16830</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38877</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>496436</t>
+          <t>496853</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>513264</t>
+          <t>513230</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146637</t>
+          <t>146605</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161683</t>
+          <t>161564</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>649159</t>
+          <t>649507</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>671325</t>
+          <t>671206</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15780</t>
+          <t>15757</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35553</t>
+          <t>35539</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20849</t>
+          <t>21161</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45381</t>
+          <t>43988</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40314</t>
+          <t>40507</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70302</t>
+          <t>70871</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1114085</t>
+          <t>1114099</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1133858</t>
+          <t>1133881</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>780495</t>
+          <t>781888</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>805027</t>
+          <t>804715</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1905212</t>
+          <t>1904643</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1935200</t>
+          <t>1935007</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17212</t>
+          <t>18019</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37819</t>
+          <t>37747</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16902</t>
+          <t>17768</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39654</t>
+          <t>39252</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40250</t>
+          <t>38240</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69233</t>
+          <t>67891</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>582887</t>
+          <t>582959</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>603494</t>
+          <t>602687</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>698590</t>
+          <t>698992</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>721342</t>
+          <t>720476</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1289717</t>
+          <t>1291059</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1318700</t>
+          <t>1320710</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36448</t>
+          <t>37772</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>66754</t>
+          <t>68176</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36500</t>
+          <t>37434</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67508</t>
+          <t>66505</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281195</t>
+          <t>281671</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1015271</t>
+          <t>1013849</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1045577</t>
+          <t>1044253</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1301662</t>
+          <t>1302665</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1332670</t>
+          <t>1331736</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>78676</t>
+          <t>78173</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>118530</t>
+          <t>118542</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>121427</t>
+          <t>119127</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>171555</t>
+          <t>169373</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>213182</t>
+          <t>211136</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>276902</t>
+          <t>275676</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3267192</t>
+          <t>3267180</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3307046</t>
+          <t>3307549</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3360041</t>
+          <t>3362223</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3410169</t>
+          <t>3412469</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6640416</t>
+          <t>6641642</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6704136</t>
+          <t>6706182</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>36548</t>
+          <t>37596</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27951</t>
+          <t>27413</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48348</t>
+          <t>47951</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19614</t>
+          <t>22091</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13970</t>
+          <t>15858</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26946</t>
+          <t>30093</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>56162</t>
+          <t>59687</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44935</t>
+          <t>47837</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68404</t>
+          <t>71953</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>468664</t>
+          <t>513022</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>456864</t>
+          <t>502667</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>477261</t>
+          <t>523205</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>427853</t>
+          <t>466320</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>420521</t>
+          <t>458318</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>433497</t>
+          <t>472553</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>896517</t>
+          <t>979342</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>884275</t>
+          <t>967076</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>907744</t>
+          <t>991192</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26106</t>
+          <t>27143</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18329</t>
+          <t>19096</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36883</t>
+          <t>38086</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18652</t>
+          <t>19805</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13184</t>
+          <t>14082</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26718</t>
+          <t>27619</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>44757</t>
+          <t>46948</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33312</t>
+          <t>36551</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56072</t>
+          <t>59375</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>426107</t>
+          <t>456069</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415330</t>
+          <t>445126</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>433884</t>
+          <t>464116</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>363928</t>
+          <t>403338</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>355862</t>
+          <t>395524</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369396</t>
+          <t>409061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>790036</t>
+          <t>859407</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>778721</t>
+          <t>846980</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>801481</t>
+          <t>869804</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>34719</t>
+          <t>36904</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13011</t>
+          <t>27177</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60909</t>
+          <t>48195</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>19123</t>
+          <t>21123</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13908</t>
+          <t>15741</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25495</t>
+          <t>28618</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>53842</t>
+          <t>58027</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23751</t>
+          <t>46806</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80450</t>
+          <t>72630</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>633545</t>
+          <t>434708</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>607355</t>
+          <t>423417</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>655253</t>
+          <t>444435</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>147788</t>
+          <t>166374</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141416</t>
+          <t>158879</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153003</t>
+          <t>171756</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>781333</t>
+          <t>601082</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>754725</t>
+          <t>586479</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>811424</t>
+          <t>612303</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>92,9%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>66710</t>
+          <t>74903</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53381</t>
+          <t>61795</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81666</t>
+          <t>91212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>56135</t>
+          <t>60601</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26109</t>
+          <t>50395</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76642</t>
+          <t>74080</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>122845</t>
+          <t>135504</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83707</t>
+          <t>117516</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>145208</t>
+          <t>155283</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>968109</t>
+          <t>1056940</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>953153</t>
+          <t>1040631</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>981438</t>
+          <t>1070048</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>921393</t>
+          <t>800014</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>900886</t>
+          <t>786535</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>951419</t>
+          <t>810220</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1889502</t>
+          <t>1856954</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1867139</t>
+          <t>1837175</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1928640</t>
+          <t>1874942</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>35048</t>
+          <t>34661</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24361</t>
+          <t>25573</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54376</t>
+          <t>47618</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>92396</t>
+          <t>101559</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67696</t>
+          <t>87465</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>109660</t>
+          <t>115463</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>127444</t>
+          <t>136221</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101696</t>
+          <t>120525</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>150600</t>
+          <t>155852</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>439001</t>
+          <t>532315</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>419673</t>
+          <t>519358</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>449688</t>
+          <t>541403</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>746600</t>
+          <t>728568</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>729336</t>
+          <t>714664</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>771300</t>
+          <t>742662</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1185601</t>
+          <t>1260882</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1162445</t>
+          <t>1241251</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1211349</t>
+          <t>1276578</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>91,37%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>8686</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>76788</t>
+          <t>83344</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>65039</t>
+          <t>70298</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>89369</t>
+          <t>98960</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,17 +10418,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>80405</t>
+          <t>86871</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67558</t>
+          <t>74272</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>94384</t>
+          <t>101474</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>236890</t>
+          <t>233702</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>231567</t>
+          <t>228542</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239292</t>
+          <t>235866</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>683364</t>
+          <t>759649</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>670783</t>
+          <t>744033</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>695113</t>
+          <t>772695</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,17 +10531,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>920254</t>
+          <t>993350</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>906275</t>
+          <t>978747</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>933101</t>
+          <t>1005949</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,12%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>202748</t>
+          <t>214733</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>159567</t>
+          <t>190348</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>235617</t>
+          <t>241997</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>282707</t>
+          <t>308523</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>226022</t>
+          <t>283811</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>314157</t>
+          <t>336202</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>485455</t>
+          <t>523257</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>418661</t>
+          <t>485893</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>532388</t>
+          <t>560702</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3172316</t>
+          <t>3226755</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3139447</t>
+          <t>3199491</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3215497</t>
+          <t>3251140</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3290927</t>
+          <t>3324263</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3259477</t>
+          <t>3296584</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3347612</t>
+          <t>3348975</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6463242</t>
+          <t>6551018</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6416309</t>
+          <t>6513573</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6530036</t>
+          <t>6588382</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,13%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3375064</t>
+          <t>3441488</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3375064</t>
+          <t>3441488</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3375064</t>
+          <t>3441488</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3573634</t>
+          <t>3632786</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3573634</t>
+          <t>3632786</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3573634</t>
+          <t>3632786</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6948697</t>
+          <t>7074275</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6948697</t>
+          <t>7074275</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6948697</t>
+          <t>7074275</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
